--- a/01-AI营销/04-选品库/C端/01-疗愈水晶手链/02-竞争对手分析/竞争对手分析.xlsx
+++ b/01-AI营销/04-选品库/C端/01-疗愈水晶手链/02-竞争对手分析/竞争对手分析.xlsx
@@ -8,9 +8,10 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="竞品总览" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Type1-水晶电商对比" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Type2-灵性媒体对比" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="研究优先级" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="竞品发现池" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Type1-水晶电商对比" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Type2-灵性媒体对比" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="研究优先级" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,7 +21,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -48,8 +49,30 @@
       <b val="1"/>
       <sz val="14"/>
     </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="001F4E79"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00C00000"/>
+      <sz val="14"/>
+    </font>
   </fonts>
-  <fills count="11">
+  <fills count="14">
     <fill>
       <patternFill/>
     </fill>
@@ -110,6 +133,24 @@
         <bgColor rgb="00EAECEE"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="004472C4"/>
+        <bgColor rgb="004472C4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C00000"/>
+        <bgColor rgb="00C00000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+        <bgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -129,7 +170,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -163,6 +204,20 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -530,7 +585,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N17"/>
+  <dimension ref="A1:N28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1592,6 +1647,736 @@
         </is>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" s="13" t="inlineStr">
+        <is>
+          <t>Type 1: 水晶电商</t>
+        </is>
+      </c>
+      <c r="B18" s="13" t="inlineStr">
+        <is>
+          <t>healingcrystals.com</t>
+        </is>
+      </c>
+      <c r="C18" s="13" t="inlineStr">
+        <is>
+          <t>Healing Crystals</t>
+        </is>
+      </c>
+      <c r="D18" s="13" t="inlineStr">
+        <is>
+          <t>待查</t>
+        </is>
+      </c>
+      <c r="E18" s="13" t="inlineStr">
+        <is>
+          <t>内容+电商(零售+批发)</t>
+        </is>
+      </c>
+      <c r="F18" s="13" t="inlineStr">
+        <is>
+          <t>待查</t>
+        </is>
+      </c>
+      <c r="G18" s="13" t="inlineStr">
+        <is>
+          <t>水晶百科+代理</t>
+        </is>
+      </c>
+      <c r="H18" s="13" t="inlineStr">
+        <is>
+          <t>待查</t>
+        </is>
+      </c>
+      <c r="I18" s="13" t="inlineStr">
+        <is>
+          <t>待查</t>
+        </is>
+      </c>
+      <c r="J18" s="13" t="inlineStr">
+        <is>
+          <t>2层</t>
+        </is>
+      </c>
+      <c r="K18" s="13" t="inlineStr">
+        <is>
+          <t>直接相关</t>
+        </is>
+      </c>
+      <c r="L18" s="13" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="M18" s="13" t="inlineStr"/>
+      <c r="N18" s="13" t="inlineStr">
+        <is>
+          <t>最老牌水晶网站</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="13" t="inlineStr">
+        <is>
+          <t>Type 1: 水晶电商</t>
+        </is>
+      </c>
+      <c r="B19" s="13" t="inlineStr">
+        <is>
+          <t>rockparadise.com</t>
+        </is>
+      </c>
+      <c r="C19" s="13" t="inlineStr">
+        <is>
+          <t>Rock Paradise</t>
+        </is>
+      </c>
+      <c r="D19" s="13" t="inlineStr">
+        <is>
+          <t>待查</t>
+        </is>
+      </c>
+      <c r="E19" s="13" t="inlineStr">
+        <is>
+          <t>电商</t>
+        </is>
+      </c>
+      <c r="F19" s="13" t="inlineStr">
+        <is>
+          <t>待查</t>
+        </is>
+      </c>
+      <c r="G19" s="13" t="inlineStr">
+        <is>
+          <t>水晶+装饰+珠宝</t>
+        </is>
+      </c>
+      <c r="H19" s="13" t="inlineStr">
+        <is>
+          <t>待查</t>
+        </is>
+      </c>
+      <c r="I19" s="13" t="inlineStr">
+        <is>
+          <t>待查</t>
+        </is>
+      </c>
+      <c r="J19" s="13" t="inlineStr">
+        <is>
+          <t>2层</t>
+        </is>
+      </c>
+      <c r="K19" s="13" t="inlineStr">
+        <is>
+          <t>直接相关</t>
+        </is>
+      </c>
+      <c r="L19" s="13" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="M19" s="13" t="inlineStr"/>
+      <c r="N19" s="13" t="inlineStr">
+        <is>
+          <t>产品线最全</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="13" t="inlineStr">
+        <is>
+          <t>Type 1: 水晶电商</t>
+        </is>
+      </c>
+      <c r="B20" s="13" t="inlineStr">
+        <is>
+          <t>moonrisecrystals.com</t>
+        </is>
+      </c>
+      <c r="C20" s="13" t="inlineStr">
+        <is>
+          <t>Moonrise Crystals</t>
+        </is>
+      </c>
+      <c r="D20" s="13" t="inlineStr">
+        <is>
+          <t>待查</t>
+        </is>
+      </c>
+      <c r="E20" s="13" t="inlineStr">
+        <is>
+          <t>内容+电商</t>
+        </is>
+      </c>
+      <c r="F20" s="13" t="inlineStr">
+        <is>
+          <t>待查</t>
+        </is>
+      </c>
+      <c r="G20" s="13" t="inlineStr">
+        <is>
+          <t>伦理采购+水晶百科</t>
+        </is>
+      </c>
+      <c r="H20" s="13" t="inlineStr">
+        <is>
+          <t>待查</t>
+        </is>
+      </c>
+      <c r="I20" s="13" t="inlineStr">
+        <is>
+          <t>待查</t>
+        </is>
+      </c>
+      <c r="J20" s="13" t="inlineStr">
+        <is>
+          <t>2层</t>
+        </is>
+      </c>
+      <c r="K20" s="13" t="inlineStr">
+        <is>
+          <t>直接相关</t>
+        </is>
+      </c>
+      <c r="L20" s="13" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="M20" s="13" t="inlineStr"/>
+      <c r="N20" s="13" t="inlineStr">
+        <is>
+          <t>伦理供应链</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="13" t="inlineStr">
+        <is>
+          <t>Type 1: 水晶电商</t>
+        </is>
+      </c>
+      <c r="B21" s="13" t="inlineStr">
+        <is>
+          <t>newmoonbeginnings.com</t>
+        </is>
+      </c>
+      <c r="C21" s="13" t="inlineStr">
+        <is>
+          <t>New Moon Beginnings</t>
+        </is>
+      </c>
+      <c r="D21" s="13" t="inlineStr">
+        <is>
+          <t>待查</t>
+        </is>
+      </c>
+      <c r="E21" s="13" t="inlineStr">
+        <is>
+          <t>内容+电商</t>
+        </is>
+      </c>
+      <c r="F21" s="13" t="inlineStr">
+        <is>
+          <t>待查</t>
+        </is>
+      </c>
+      <c r="G21" s="13" t="inlineStr">
+        <is>
+          <t>水晶+神秘学</t>
+        </is>
+      </c>
+      <c r="H21" s="13" t="inlineStr">
+        <is>
+          <t>待查</t>
+        </is>
+      </c>
+      <c r="I21" s="13" t="inlineStr">
+        <is>
+          <t>待查</t>
+        </is>
+      </c>
+      <c r="J21" s="13" t="inlineStr">
+        <is>
+          <t>2层</t>
+        </is>
+      </c>
+      <c r="K21" s="13" t="inlineStr">
+        <is>
+          <t>直接相关</t>
+        </is>
+      </c>
+      <c r="L21" s="13" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="M21" s="13" t="inlineStr"/>
+      <c r="N21" s="13" t="inlineStr">
+        <is>
+          <t>月亮主题</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="13" t="inlineStr">
+        <is>
+          <t>Type 1: 水晶电商</t>
+        </is>
+      </c>
+      <c r="B22" s="13" t="inlineStr">
+        <is>
+          <t>wildmountaincrystals.com</t>
+        </is>
+      </c>
+      <c r="C22" s="13" t="inlineStr">
+        <is>
+          <t>Wild Mountain Crystals</t>
+        </is>
+      </c>
+      <c r="D22" s="13" t="inlineStr">
+        <is>
+          <t>待查</t>
+        </is>
+      </c>
+      <c r="E22" s="13" t="inlineStr">
+        <is>
+          <t>内容+电商</t>
+        </is>
+      </c>
+      <c r="F22" s="13" t="inlineStr">
+        <is>
+          <t>待查</t>
+        </is>
+      </c>
+      <c r="G22" s="13" t="inlineStr">
+        <is>
+          <t>疗愈水晶+套装</t>
+        </is>
+      </c>
+      <c r="H22" s="13" t="inlineStr">
+        <is>
+          <t>待查</t>
+        </is>
+      </c>
+      <c r="I22" s="13" t="inlineStr">
+        <is>
+          <t>待查</t>
+        </is>
+      </c>
+      <c r="J22" s="13" t="inlineStr">
+        <is>
+          <t>2层</t>
+        </is>
+      </c>
+      <c r="K22" s="13" t="inlineStr">
+        <is>
+          <t>直接相关</t>
+        </is>
+      </c>
+      <c r="L22" s="13" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="M22" s="13" t="inlineStr"/>
+      <c r="N22" s="13" t="inlineStr">
+        <is>
+          <t>治疗定位</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="13" t="inlineStr">
+        <is>
+          <t>Type 2: 灵性媒体</t>
+        </is>
+      </c>
+      <c r="B23" s="13" t="inlineStr">
+        <is>
+          <t>tarot.com</t>
+        </is>
+      </c>
+      <c r="C23" s="13" t="inlineStr">
+        <is>
+          <t>Tarot.com</t>
+        </is>
+      </c>
+      <c r="D23" s="13" t="inlineStr">
+        <is>
+          <t>500万+</t>
+        </is>
+      </c>
+      <c r="E23" s="13" t="inlineStr">
+        <is>
+          <t>广告+订阅+虚拟服务</t>
+        </is>
+      </c>
+      <c r="F23" s="13" t="inlineStr">
+        <is>
+          <t>塔罗解读+星座运势+数字占卜</t>
+        </is>
+      </c>
+      <c r="G23" s="13" t="inlineStr">
+        <is>
+          <t>1000+</t>
+        </is>
+      </c>
+      <c r="H23" s="13" t="inlineStr">
+        <is>
+          <t>极强</t>
+        </is>
+      </c>
+      <c r="I23" s="13" t="inlineStr">
+        <is>
+          <t>多层</t>
+        </is>
+      </c>
+      <c r="J23" s="13" t="inlineStr">
+        <is>
+          <t>中(占星+水晶)</t>
+        </is>
+      </c>
+      <c r="K23" s="13" t="inlineStr">
+        <is>
+          <t>极高</t>
+        </is>
+      </c>
+      <c r="L23" s="13" t="inlineStr"/>
+      <c r="M23" s="13" t="inlineStr">
+        <is>
+          <t>全球最大塔罗占星平台</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="13" t="inlineStr">
+        <is>
+          <t>Type 2: 灵性媒体</t>
+        </is>
+      </c>
+      <c r="B24" s="13" t="inlineStr">
+        <is>
+          <t>astrologyzone.com</t>
+        </is>
+      </c>
+      <c r="C24" s="13" t="inlineStr">
+        <is>
+          <t>Astrology Zone</t>
+        </is>
+      </c>
+      <c r="D24" s="13" t="inlineStr">
+        <is>
+          <t>800万+</t>
+        </is>
+      </c>
+      <c r="E24" s="13" t="inlineStr">
+        <is>
+          <t>广告+订阅+APP</t>
+        </is>
+      </c>
+      <c r="F24" s="13" t="inlineStr">
+        <is>
+          <t>月度星座运势+年度预测</t>
+        </is>
+      </c>
+      <c r="G24" s="13" t="inlineStr">
+        <is>
+          <t>500+</t>
+        </is>
+      </c>
+      <c r="H24" s="13" t="inlineStr">
+        <is>
+          <t>极强</t>
+        </is>
+      </c>
+      <c r="I24" s="13" t="inlineStr">
+        <is>
+          <t>多层</t>
+        </is>
+      </c>
+      <c r="J24" s="13" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="K24" s="13" t="inlineStr">
+        <is>
+          <t>极高</t>
+        </is>
+      </c>
+      <c r="L24" s="13" t="inlineStr"/>
+      <c r="M24" s="13" t="inlineStr">
+        <is>
+          <t>Susan Miller IP</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="13" t="inlineStr">
+        <is>
+          <t>Type 2: 灵性媒体</t>
+        </is>
+      </c>
+      <c r="B25" s="13" t="inlineStr">
+        <is>
+          <t>foreverconscious.com</t>
+        </is>
+      </c>
+      <c r="C25" s="13" t="inlineStr">
+        <is>
+          <t>Forever Conscious</t>
+        </is>
+      </c>
+      <c r="D25" s="13" t="inlineStr">
+        <is>
+          <t>待查</t>
+        </is>
+      </c>
+      <c r="E25" s="13" t="inlineStr">
+        <is>
+          <t>广告+联盟</t>
+        </is>
+      </c>
+      <c r="F25" s="13" t="inlineStr">
+        <is>
+          <t>月相仪式+星座预测+灵性指南</t>
+        </is>
+      </c>
+      <c r="G25" s="13" t="inlineStr">
+        <is>
+          <t>500+</t>
+        </is>
+      </c>
+      <c r="H25" s="13" t="inlineStr">
+        <is>
+          <t>强</t>
+        </is>
+      </c>
+      <c r="I25" s="13" t="inlineStr">
+        <is>
+          <t>2层</t>
+        </is>
+      </c>
+      <c r="J25" s="13" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="K25" s="13" t="inlineStr">
+        <is>
+          <t>极高</t>
+        </is>
+      </c>
+      <c r="L25" s="13" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="M25" s="13" t="inlineStr">
+        <is>
+          <t>事件驱动+月相矩阵</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="13" t="inlineStr">
+        <is>
+          <t>Type 2: 灵性媒体</t>
+        </is>
+      </c>
+      <c r="B26" s="13" t="inlineStr">
+        <is>
+          <t>moonomens.com</t>
+        </is>
+      </c>
+      <c r="C26" s="13" t="inlineStr">
+        <is>
+          <t>Moon Omens</t>
+        </is>
+      </c>
+      <c r="D26" s="13" t="inlineStr">
+        <is>
+          <t>待查</t>
+        </is>
+      </c>
+      <c r="E26" s="13" t="inlineStr">
+        <is>
+          <t>广告+联盟+数字产品</t>
+        </is>
+      </c>
+      <c r="F26" s="13" t="inlineStr">
+        <is>
+          <t>月相仪式+冥想音频+日志</t>
+        </is>
+      </c>
+      <c r="G26" s="13" t="inlineStr">
+        <is>
+          <t>200+</t>
+        </is>
+      </c>
+      <c r="H26" s="13" t="inlineStr">
+        <is>
+          <t>强</t>
+        </is>
+      </c>
+      <c r="I26" s="13" t="inlineStr">
+        <is>
+          <t>2层</t>
+        </is>
+      </c>
+      <c r="J26" s="13" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="K26" s="13" t="inlineStr">
+        <is>
+          <t>极高</t>
+        </is>
+      </c>
+      <c r="L26" s="13" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="M26" s="13" t="inlineStr">
+        <is>
+          <t>月相+音频变现</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="13" t="inlineStr">
+        <is>
+          <t>Type 2: 灵性媒体</t>
+        </is>
+      </c>
+      <c r="B27" s="13" t="inlineStr">
+        <is>
+          <t>selfgazer.com</t>
+        </is>
+      </c>
+      <c r="C27" s="13" t="inlineStr">
+        <is>
+          <t>Selfgazer</t>
+        </is>
+      </c>
+      <c r="D27" s="13" t="inlineStr">
+        <is>
+          <t>待查</t>
+        </is>
+      </c>
+      <c r="E27" s="13" t="inlineStr">
+        <is>
+          <t>广告+虚拟服务</t>
+        </is>
+      </c>
+      <c r="F27" s="13" t="inlineStr">
+        <is>
+          <t>交互式塔罗+星图+易经</t>
+        </is>
+      </c>
+      <c r="G27" s="13" t="inlineStr">
+        <is>
+          <t>50+</t>
+        </is>
+      </c>
+      <c r="H27" s="13" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="I27" s="13" t="inlineStr">
+        <is>
+          <t>2层</t>
+        </is>
+      </c>
+      <c r="J27" s="13" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="K27" s="13" t="inlineStr">
+        <is>
+          <t>极高</t>
+        </is>
+      </c>
+      <c r="L27" s="13" t="inlineStr"/>
+      <c r="M27" s="13" t="inlineStr">
+        <is>
+          <t>交互工具标杆</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="13" t="inlineStr">
+        <is>
+          <t>Type 2: 灵性媒体</t>
+        </is>
+      </c>
+      <c r="B28" s="13" t="inlineStr">
+        <is>
+          <t>mindvalley.com</t>
+        </is>
+      </c>
+      <c r="C28" s="13" t="inlineStr">
+        <is>
+          <t>Mindvalley</t>
+        </is>
+      </c>
+      <c r="D28" s="13" t="inlineStr">
+        <is>
+          <t>1000万+</t>
+        </is>
+      </c>
+      <c r="E28" s="13" t="inlineStr">
+        <is>
+          <t>课程+会员+联盟</t>
+        </is>
+      </c>
+      <c r="F28" s="13" t="inlineStr">
+        <is>
+          <t>灵性课程+博客</t>
+        </is>
+      </c>
+      <c r="G28" s="13" t="inlineStr">
+        <is>
+          <t>大</t>
+        </is>
+      </c>
+      <c r="H28" s="13" t="inlineStr">
+        <is>
+          <t>极强</t>
+        </is>
+      </c>
+      <c r="I28" s="13" t="inlineStr">
+        <is>
+          <t>多层</t>
+        </is>
+      </c>
+      <c r="J28" s="13" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="K28" s="13" t="inlineStr">
+        <is>
+          <t>极高</t>
+        </is>
+      </c>
+      <c r="L28" s="13" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="M28" s="13" t="inlineStr">
+        <is>
+          <t>课程变现标杆</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:N1"/>
@@ -1601,6 +2386,2064 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H51"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="48" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="28" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="28" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="14" t="inlineStr">
+        <is>
+          <t>竞品发现池 - SERP挖掘结果 (2026-05-02)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="15" t="inlineStr">
+        <is>
+          <t>网址</t>
+        </is>
+      </c>
+      <c r="B2" s="15" t="inlineStr">
+        <is>
+          <t>网站名称</t>
+        </is>
+      </c>
+      <c r="C2" s="15" t="inlineStr">
+        <is>
+          <t>简介</t>
+        </is>
+      </c>
+      <c r="D2" s="15" t="inlineStr">
+        <is>
+          <t>与现有竞品列表重复</t>
+        </is>
+      </c>
+      <c r="E2" s="15" t="inlineStr">
+        <is>
+          <t>初步分类</t>
+        </is>
+      </c>
+      <c r="F2" s="15" t="inlineStr">
+        <is>
+          <t>建议操作</t>
+        </is>
+      </c>
+      <c r="G2" s="15" t="inlineStr">
+        <is>
+          <t>优先级</t>
+        </is>
+      </c>
+      <c r="H2" s="15" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>https://healingcrystals.com</t>
+        </is>
+      </c>
+      <c r="B3" s="13" t="inlineStr">
+        <is>
+          <t>Healing Crystals</t>
+        </is>
+      </c>
+      <c r="C3" s="13" t="inlineStr">
+        <is>
+          <t>Retail &amp; wholesale, free resources, metaphysical guide</t>
+        </is>
+      </c>
+      <c r="D3" s="13" t="inlineStr">
+        <is>
+          <t>新发现</t>
+        </is>
+      </c>
+      <c r="E3" s="13" t="inlineStr">
+        <is>
+          <t>高价值目标</t>
+        </is>
+      </c>
+      <c r="F3" s="13" t="inlineStr">
+        <is>
+          <t>添加到竞品总览并深入研究</t>
+        </is>
+      </c>
+      <c r="G3" s="13" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H3" s="13" t="inlineStr">
+        <is>
+          <t>最老牌水晶网站之一</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="13" t="inlineStr">
+        <is>
+          <t>https://rockparadise.com</t>
+        </is>
+      </c>
+      <c r="B4" s="13" t="inlineStr">
+        <is>
+          <t>Rock Paradise</t>
+        </is>
+      </c>
+      <c r="C4" s="13" t="inlineStr">
+        <is>
+          <t>One of the largest crystal collections online</t>
+        </is>
+      </c>
+      <c r="D4" s="13" t="inlineStr">
+        <is>
+          <t>新发现</t>
+        </is>
+      </c>
+      <c r="E4" s="13" t="inlineStr">
+        <is>
+          <t>高价值目标</t>
+        </is>
+      </c>
+      <c r="F4" s="13" t="inlineStr">
+        <is>
+          <t>添加到竞品总览并深入研究</t>
+        </is>
+      </c>
+      <c r="G4" s="13" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H4" s="13" t="inlineStr">
+        <is>
+          <t>产品线最全面</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="13" t="inlineStr">
+        <is>
+          <t>https://moonrisecrystals.com</t>
+        </is>
+      </c>
+      <c r="B5" s="13" t="inlineStr">
+        <is>
+          <t>Moonrise Crystals</t>
+        </is>
+      </c>
+      <c r="C5" s="13" t="inlineStr">
+        <is>
+          <t>Ethical sourcing, hand-selected stones</t>
+        </is>
+      </c>
+      <c r="D5" s="13" t="inlineStr">
+        <is>
+          <t>新发现</t>
+        </is>
+      </c>
+      <c r="E5" s="13" t="inlineStr">
+        <is>
+          <t>高价值目标</t>
+        </is>
+      </c>
+      <c r="F5" s="13" t="inlineStr">
+        <is>
+          <t>添加到竞品总览并深入研究</t>
+        </is>
+      </c>
+      <c r="G5" s="13" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H5" s="13" t="inlineStr">
+        <is>
+          <t>伦理供应链差异化</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="13" t="inlineStr">
+        <is>
+          <t>https://sagegoddess.com</t>
+        </is>
+      </c>
+      <c r="B6" s="13" t="inlineStr">
+        <is>
+          <t>Sage Goddess</t>
+        </is>
+      </c>
+      <c r="C6" s="13" t="inlineStr">
+        <is>
+          <t>World largest healing crystals + chakra tools + perfumes</t>
+        </is>
+      </c>
+      <c r="D6" s="13" t="inlineStr">
+        <is>
+          <t>已存在</t>
+        </is>
+      </c>
+      <c r="E6" s="13" t="inlineStr">
+        <is>
+          <t>小型站点</t>
+        </is>
+      </c>
+      <c r="F6" s="13" t="inlineStr">
+        <is>
+          <t>可选参考</t>
+        </is>
+      </c>
+      <c r="G6" s="13" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="H6" s="13" t="inlineStr">
+        <is>
+          <t>广泛的产品线</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="13" t="inlineStr">
+        <is>
+          <t>https://wildmountaincrystals.com</t>
+        </is>
+      </c>
+      <c r="B7" s="13" t="inlineStr">
+        <is>
+          <t>Wild Mountain Crystals</t>
+        </is>
+      </c>
+      <c r="C7" s="13" t="inlineStr">
+        <is>
+          <t>Crystals for calm, anxiety, gift sets</t>
+        </is>
+      </c>
+      <c r="D7" s="13" t="inlineStr">
+        <is>
+          <t>新发现</t>
+        </is>
+      </c>
+      <c r="E7" s="13" t="inlineStr">
+        <is>
+          <t>高价值目标</t>
+        </is>
+      </c>
+      <c r="F7" s="13" t="inlineStr">
+        <is>
+          <t>添加到竞品总览并深入研究</t>
+        </is>
+      </c>
+      <c r="G7" s="13" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H7" s="13" t="inlineStr">
+        <is>
+          <t>治疗向定位精准</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="13" t="inlineStr">
+        <is>
+          <t>https://sacredcrystals.rocks</t>
+        </is>
+      </c>
+      <c r="B8" s="13" t="inlineStr">
+        <is>
+          <t>Sacred Crystals</t>
+        </is>
+      </c>
+      <c r="C8" s="13" t="inlineStr">
+        <is>
+          <t>Ethically sourced, jewelry &amp; metaphysical supplies</t>
+        </is>
+      </c>
+      <c r="D8" s="13" t="inlineStr">
+        <is>
+          <t>新发现</t>
+        </is>
+      </c>
+      <c r="E8" s="13" t="inlineStr">
+        <is>
+          <t>中等规模</t>
+        </is>
+      </c>
+      <c r="F8" s="13" t="inlineStr">
+        <is>
+          <t>快速浏览参考</t>
+        </is>
+      </c>
+      <c r="G8" s="13" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H8" s="13" t="inlineStr">
+        <is>
+          <t>伦理差异化</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="13" t="inlineStr">
+        <is>
+          <t>https://newmoonbeginnings.com</t>
+        </is>
+      </c>
+      <c r="B9" s="13" t="inlineStr">
+        <is>
+          <t>New Moon Beginnings</t>
+        </is>
+      </c>
+      <c r="C9" s="13" t="inlineStr">
+        <is>
+          <t>Online Crystal Shop &amp; Metaphysical Store</t>
+        </is>
+      </c>
+      <c r="D9" s="13" t="inlineStr">
+        <is>
+          <t>新发现</t>
+        </is>
+      </c>
+      <c r="E9" s="13" t="inlineStr">
+        <is>
+          <t>高价值目标</t>
+        </is>
+      </c>
+      <c r="F9" s="13" t="inlineStr">
+        <is>
+          <t>添加到竞品总览并深入研究</t>
+        </is>
+      </c>
+      <c r="G9" s="13" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H9" s="13" t="inlineStr">
+        <is>
+          <t>月亮主题差异化</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="13" t="inlineStr">
+        <is>
+          <t>https://contempocrystals.com</t>
+        </is>
+      </c>
+      <c r="B10" s="13" t="inlineStr">
+        <is>
+          <t>Contempo Crystals</t>
+        </is>
+      </c>
+      <c r="C10" s="13" t="inlineStr">
+        <is>
+          <t>Natural crystal jewelry - rings, bracelets, necklaces</t>
+        </is>
+      </c>
+      <c r="D10" s="13" t="inlineStr">
+        <is>
+          <t>新发现</t>
+        </is>
+      </c>
+      <c r="E10" s="13" t="inlineStr">
+        <is>
+          <t>中等规模</t>
+        </is>
+      </c>
+      <c r="F10" s="13" t="inlineStr">
+        <is>
+          <t>快速浏览参考</t>
+        </is>
+      </c>
+      <c r="G10" s="13" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H10" s="13" t="inlineStr">
+        <is>
+          <t>珠宝专精</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="13" t="inlineStr">
+        <is>
+          <t>https://happysoulcrystals.com</t>
+        </is>
+      </c>
+      <c r="B11" s="13" t="inlineStr">
+        <is>
+          <t>Happy Soul Crystals</t>
+        </is>
+      </c>
+      <c r="C11" s="13" t="inlineStr">
+        <is>
+          <t>Crystal bracelets, spiritual gifts</t>
+        </is>
+      </c>
+      <c r="D11" s="13" t="inlineStr">
+        <is>
+          <t>新发现</t>
+        </is>
+      </c>
+      <c r="E11" s="13" t="inlineStr">
+        <is>
+          <t>中等规模</t>
+        </is>
+      </c>
+      <c r="F11" s="13" t="inlineStr">
+        <is>
+          <t>快速浏览参考</t>
+        </is>
+      </c>
+      <c r="G11" s="13" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H11" s="13" t="inlineStr">
+        <is>
+          <t>手链专精</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="13" t="inlineStr">
+        <is>
+          <t>https://sedonacrystalvortex.com</t>
+        </is>
+      </c>
+      <c r="B12" s="13" t="inlineStr">
+        <is>
+          <t>Sedona Crystal Vortex</t>
+        </is>
+      </c>
+      <c r="C12" s="13" t="inlineStr">
+        <is>
+          <t>Healing crystal bracelets, Sedona-based</t>
+        </is>
+      </c>
+      <c r="D12" s="13" t="inlineStr">
+        <is>
+          <t>新发现</t>
+        </is>
+      </c>
+      <c r="E12" s="13" t="inlineStr">
+        <is>
+          <t>中等规模</t>
+        </is>
+      </c>
+      <c r="F12" s="13" t="inlineStr">
+        <is>
+          <t>快速浏览参考</t>
+        </is>
+      </c>
+      <c r="G12" s="13" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H12" s="13" t="inlineStr">
+        <is>
+          <t>地理位置差异化</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="13" t="inlineStr">
+        <is>
+          <t>https://rockthiswaycrystalshop.com</t>
+        </is>
+      </c>
+      <c r="B13" s="13" t="inlineStr">
+        <is>
+          <t>Rock This Way</t>
+        </is>
+      </c>
+      <c r="C13" s="13" t="inlineStr">
+        <is>
+          <t>Crystal jewelry &amp; zodiac bracelets</t>
+        </is>
+      </c>
+      <c r="D13" s="13" t="inlineStr">
+        <is>
+          <t>新发现</t>
+        </is>
+      </c>
+      <c r="E13" s="13" t="inlineStr">
+        <is>
+          <t>中等规模</t>
+        </is>
+      </c>
+      <c r="F13" s="13" t="inlineStr">
+        <is>
+          <t>快速浏览参考</t>
+        </is>
+      </c>
+      <c r="G13" s="13" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H13" s="13" t="inlineStr">
+        <is>
+          <t>星座差异化</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="13" t="inlineStr">
+        <is>
+          <t>https://zenjewelz.com</t>
+        </is>
+      </c>
+      <c r="B14" s="13" t="inlineStr">
+        <is>
+          <t>ZenJewelz</t>
+        </is>
+      </c>
+      <c r="C14" s="13" t="inlineStr">
+        <is>
+          <t>Handcrafted healing crystal jewelry &amp; beaded bracelets</t>
+        </is>
+      </c>
+      <c r="D14" s="13" t="inlineStr">
+        <is>
+          <t>新发现</t>
+        </is>
+      </c>
+      <c r="E14" s="13" t="inlineStr">
+        <is>
+          <t>小型站点</t>
+        </is>
+      </c>
+      <c r="F14" s="13" t="inlineStr">
+        <is>
+          <t>可选参考</t>
+        </is>
+      </c>
+      <c r="G14" s="13" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="H14" s="13" t="inlineStr">
+        <is>
+          <t>手工制作差异化</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="13" t="inlineStr">
+        <is>
+          <t>https://consciousitems.com</t>
+        </is>
+      </c>
+      <c r="B15" s="13" t="inlineStr">
+        <is>
+          <t>Conscious Items</t>
+        </is>
+      </c>
+      <c r="C15" s="13" t="inlineStr">
+        <is>
+          <t>Healing gemstone &amp; crystal bracelets</t>
+        </is>
+      </c>
+      <c r="D15" s="13" t="inlineStr">
+        <is>
+          <t>新发现</t>
+        </is>
+      </c>
+      <c r="E15" s="13" t="inlineStr">
+        <is>
+          <t>中等规模</t>
+        </is>
+      </c>
+      <c r="F15" s="13" t="inlineStr">
+        <is>
+          <t>快速浏览参考</t>
+        </is>
+      </c>
+      <c r="G15" s="13" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H15" s="13" t="inlineStr">
+        <is>
+          <t>产品线单一</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="13" t="inlineStr">
+        <is>
+          <t>https://injewels.net</t>
+        </is>
+      </c>
+      <c r="B16" s="13" t="inlineStr">
+        <is>
+          <t>InJewels</t>
+        </is>
+      </c>
+      <c r="C16" s="13" t="inlineStr">
+        <is>
+          <t>Spirituality growth crystal &amp; stone bracelets</t>
+        </is>
+      </c>
+      <c r="D16" s="13" t="inlineStr">
+        <is>
+          <t>新发现</t>
+        </is>
+      </c>
+      <c r="E16" s="13" t="inlineStr">
+        <is>
+          <t>小型站点</t>
+        </is>
+      </c>
+      <c r="F16" s="13" t="inlineStr">
+        <is>
+          <t>可选参考</t>
+        </is>
+      </c>
+      <c r="G16" s="13" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="H16" s="13" t="inlineStr">
+        <is>
+          <t>小型站</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="13" t="inlineStr">
+        <is>
+          <t>https://potalastore.com</t>
+        </is>
+      </c>
+      <c r="B17" s="13" t="inlineStr">
+        <is>
+          <t>PotalaStore</t>
+        </is>
+      </c>
+      <c r="C17" s="13" t="inlineStr">
+        <is>
+          <t>Spiritual healing crystal bracelets, chakra &amp; Buddha</t>
+        </is>
+      </c>
+      <c r="D17" s="13" t="inlineStr">
+        <is>
+          <t>新发现</t>
+        </is>
+      </c>
+      <c r="E17" s="13" t="inlineStr">
+        <is>
+          <t>小型站点</t>
+        </is>
+      </c>
+      <c r="F17" s="13" t="inlineStr">
+        <is>
+          <t>可选参考</t>
+        </is>
+      </c>
+      <c r="G17" s="13" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="H17" s="13" t="inlineStr">
+        <is>
+          <t>佛教元素</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="13" t="inlineStr">
+        <is>
+          <t>https://sagecrystals.com</t>
+        </is>
+      </c>
+      <c r="B18" s="13" t="inlineStr">
+        <is>
+          <t>Sage Crystals</t>
+        </is>
+      </c>
+      <c r="C18" s="13" t="inlineStr">
+        <is>
+          <t>Anti-anxiety, peace &amp; calm crystals</t>
+        </is>
+      </c>
+      <c r="D18" s="13" t="inlineStr">
+        <is>
+          <t>新发现</t>
+        </is>
+      </c>
+      <c r="E18" s="13" t="inlineStr">
+        <is>
+          <t>中等规模</t>
+        </is>
+      </c>
+      <c r="F18" s="13" t="inlineStr">
+        <is>
+          <t>快速浏览参考</t>
+        </is>
+      </c>
+      <c r="G18" s="13" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H18" s="13" t="inlineStr">
+        <is>
+          <t>治疗定位精准</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="13" t="inlineStr">
+        <is>
+          <t>https://eastmeetswestusa.com</t>
+        </is>
+      </c>
+      <c r="B19" s="13" t="inlineStr">
+        <is>
+          <t>East Meets West</t>
+        </is>
+      </c>
+      <c r="C19" s="13" t="inlineStr">
+        <is>
+          <t>Crystals for anxiety, authentic stones</t>
+        </is>
+      </c>
+      <c r="D19" s="13" t="inlineStr">
+        <is>
+          <t>新发现</t>
+        </is>
+      </c>
+      <c r="E19" s="13" t="inlineStr">
+        <is>
+          <t>中等规模</t>
+        </is>
+      </c>
+      <c r="F19" s="13" t="inlineStr">
+        <is>
+          <t>快速浏览参考</t>
+        </is>
+      </c>
+      <c r="G19" s="13" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H19" s="13" t="inlineStr">
+        <is>
+          <t>东西方融合理念</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="13" t="inlineStr">
+        <is>
+          <t>https://magiccrystals.com</t>
+        </is>
+      </c>
+      <c r="B20" s="13" t="inlineStr">
+        <is>
+          <t>Magic Crystals</t>
+        </is>
+      </c>
+      <c r="C20" s="13" t="inlineStr">
+        <is>
+          <t>Healing crystals kit, anxiety crystals</t>
+        </is>
+      </c>
+      <c r="D20" s="13" t="inlineStr">
+        <is>
+          <t>新发现</t>
+        </is>
+      </c>
+      <c r="E20" s="13" t="inlineStr">
+        <is>
+          <t>中等规模</t>
+        </is>
+      </c>
+      <c r="F20" s="13" t="inlineStr">
+        <is>
+          <t>快速浏览参考</t>
+        </is>
+      </c>
+      <c r="G20" s="13" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H20" s="13" t="inlineStr">
+        <is>
+          <t>套装产品</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="13" t="inlineStr">
+        <is>
+          <t>https://crystaldestiny.com</t>
+        </is>
+      </c>
+      <c r="B21" s="13" t="inlineStr">
+        <is>
+          <t>Crystal Destiny</t>
+        </is>
+      </c>
+      <c r="C21" s="13" t="inlineStr">
+        <is>
+          <t>Anxiety relief crystals - Amethyst, Selenite &amp; Howlite</t>
+        </is>
+      </c>
+      <c r="D21" s="13" t="inlineStr">
+        <is>
+          <t>新发现</t>
+        </is>
+      </c>
+      <c r="E21" s="13" t="inlineStr">
+        <is>
+          <t>小型站点</t>
+        </is>
+      </c>
+      <c r="F21" s="13" t="inlineStr">
+        <is>
+          <t>可选参考</t>
+        </is>
+      </c>
+      <c r="G21" s="13" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="H21" s="13" t="inlineStr">
+        <is>
+          <t>小型站</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="13" t="inlineStr">
+        <is>
+          <t>https://rockswithsass.com</t>
+        </is>
+      </c>
+      <c r="B22" s="13" t="inlineStr">
+        <is>
+          <t>Rocks with Sass</t>
+        </is>
+      </c>
+      <c r="C22" s="13" t="inlineStr">
+        <is>
+          <t>Stress and anxiety crystal set</t>
+        </is>
+      </c>
+      <c r="D22" s="13" t="inlineStr">
+        <is>
+          <t>新发现</t>
+        </is>
+      </c>
+      <c r="E22" s="13" t="inlineStr">
+        <is>
+          <t>中等规模</t>
+        </is>
+      </c>
+      <c r="F22" s="13" t="inlineStr">
+        <is>
+          <t>快速浏览参考</t>
+        </is>
+      </c>
+      <c r="G22" s="13" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H22" s="13" t="inlineStr">
+        <is>
+          <t>品牌个性化</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="13" t="inlineStr">
+        <is>
+          <t>https://reikicrystalproducts.com</t>
+        </is>
+      </c>
+      <c r="B23" s="13" t="inlineStr">
+        <is>
+          <t>Reiki Crystal Products</t>
+        </is>
+      </c>
+      <c r="C23" s="13" t="inlineStr">
+        <is>
+          <t>Healing crystals for Reiki, crystal therapy</t>
+        </is>
+      </c>
+      <c r="D23" s="13" t="inlineStr">
+        <is>
+          <t>新发现</t>
+        </is>
+      </c>
+      <c r="E23" s="13" t="inlineStr">
+        <is>
+          <t>中等规模</t>
+        </is>
+      </c>
+      <c r="F23" s="13" t="inlineStr">
+        <is>
+          <t>快速浏览参考</t>
+        </is>
+      </c>
+      <c r="G23" s="13" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H23" s="13" t="inlineStr">
+        <is>
+          <t>灵气定位</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="13" t="inlineStr">
+        <is>
+          <t>https://orgonitecrystals.com</t>
+        </is>
+      </c>
+      <c r="B24" s="13" t="inlineStr">
+        <is>
+          <t>Orgonite Crystals</t>
+        </is>
+      </c>
+      <c r="C24" s="13" t="inlineStr">
+        <is>
+          <t>7 Chakra reiki crystal bracelet</t>
+        </is>
+      </c>
+      <c r="D24" s="13" t="inlineStr">
+        <is>
+          <t>新发现</t>
+        </is>
+      </c>
+      <c r="E24" s="13" t="inlineStr">
+        <is>
+          <t>小型站点</t>
+        </is>
+      </c>
+      <c r="F24" s="13" t="inlineStr">
+        <is>
+          <t>可选参考</t>
+        </is>
+      </c>
+      <c r="G24" s="13" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="H24" s="13" t="inlineStr">
+        <is>
+          <t>单品类站</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="13" t="inlineStr">
+        <is>
+          <t>https://energyartistjulia.com</t>
+        </is>
+      </c>
+      <c r="B25" s="13" t="inlineStr">
+        <is>
+          <t>Energy Artist Julia</t>
+        </is>
+      </c>
+      <c r="C25" s="13" t="inlineStr">
+        <is>
+          <t>Guaranteed authentic chakra healing stones</t>
+        </is>
+      </c>
+      <c r="D25" s="13" t="inlineStr">
+        <is>
+          <t>新发现</t>
+        </is>
+      </c>
+      <c r="E25" s="13" t="inlineStr">
+        <is>
+          <t>小型站点</t>
+        </is>
+      </c>
+      <c r="F25" s="13" t="inlineStr">
+        <is>
+          <t>可选参考</t>
+        </is>
+      </c>
+      <c r="G25" s="13" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="H25" s="13" t="inlineStr">
+        <is>
+          <t>艺术家IP</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="13" t="inlineStr">
+        <is>
+          <t>https://shop.drneetikaushik.com</t>
+        </is>
+      </c>
+      <c r="B26" s="13" t="inlineStr">
+        <is>
+          <t>Dr. Neeti Kaushik</t>
+        </is>
+      </c>
+      <c r="C26" s="13" t="inlineStr">
+        <is>
+          <t>7 Chakra healing products - bracelets, malas, pendants</t>
+        </is>
+      </c>
+      <c r="D26" s="13" t="inlineStr">
+        <is>
+          <t>新发现</t>
+        </is>
+      </c>
+      <c r="E26" s="13" t="inlineStr">
+        <is>
+          <t>小型站点</t>
+        </is>
+      </c>
+      <c r="F26" s="13" t="inlineStr">
+        <is>
+          <t>可选参考</t>
+        </is>
+      </c>
+      <c r="G26" s="13" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="H26" s="13" t="inlineStr">
+        <is>
+          <t>专家IP</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="13" t="inlineStr">
+        <is>
+          <t>https://crystalauras.com</t>
+        </is>
+      </c>
+      <c r="B27" s="13" t="inlineStr">
+        <is>
+          <t>Crystal Auras</t>
+        </is>
+      </c>
+      <c r="C27" s="13" t="inlineStr">
+        <is>
+          <t>Crystals for anxiety crystal kit</t>
+        </is>
+      </c>
+      <c r="D27" s="13" t="inlineStr">
+        <is>
+          <t>新发现</t>
+        </is>
+      </c>
+      <c r="E27" s="13" t="inlineStr">
+        <is>
+          <t>小型站点</t>
+        </is>
+      </c>
+      <c r="F27" s="13" t="inlineStr">
+        <is>
+          <t>可选参考</t>
+        </is>
+      </c>
+      <c r="G27" s="13" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="H27" s="13" t="inlineStr">
+        <is>
+          <t>小型站</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="13" t="inlineStr">
+        <is>
+          <t>https://lunanorte.co</t>
+        </is>
+      </c>
+      <c r="B28" s="13" t="inlineStr">
+        <is>
+          <t>Luna Norte</t>
+        </is>
+      </c>
+      <c r="C28" s="13" t="inlineStr">
+        <is>
+          <t>Genuine crystal curios, jewelry</t>
+        </is>
+      </c>
+      <c r="D28" s="13" t="inlineStr">
+        <is>
+          <t>新发现</t>
+        </is>
+      </c>
+      <c r="E28" s="13" t="inlineStr">
+        <is>
+          <t>中等规模</t>
+        </is>
+      </c>
+      <c r="F28" s="13" t="inlineStr">
+        <is>
+          <t>快速浏览参考</t>
+        </is>
+      </c>
+      <c r="G28" s="13" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H28" s="13" t="inlineStr">
+        <is>
+          <t>设计感好</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="13" t="inlineStr">
+        <is>
+          <t>https://crystalcandlehub.com</t>
+        </is>
+      </c>
+      <c r="B29" s="13" t="inlineStr">
+        <is>
+          <t>Crystal Candle Hub</t>
+        </is>
+      </c>
+      <c r="C29" s="13" t="inlineStr">
+        <is>
+          <t>Reiki natural stone 7 chakra healing crystal bracelet</t>
+        </is>
+      </c>
+      <c r="D29" s="13" t="inlineStr">
+        <is>
+          <t>新发现</t>
+        </is>
+      </c>
+      <c r="E29" s="13" t="inlineStr">
+        <is>
+          <t>小型站点</t>
+        </is>
+      </c>
+      <c r="F29" s="13" t="inlineStr">
+        <is>
+          <t>可选参考</t>
+        </is>
+      </c>
+      <c r="G29" s="13" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="H29" s="13" t="inlineStr">
+        <is>
+          <t>水晶+蜡烛交叉销售</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="16" t="inlineStr">
+        <is>
+          <t>Type 2: 灵性生活方式内容媒体 - SERP挖掘结果 (2026-05-02)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="17" t="inlineStr">
+        <is>
+          <t>网址</t>
+        </is>
+      </c>
+      <c r="B32" s="17" t="inlineStr">
+        <is>
+          <t>网站名称</t>
+        </is>
+      </c>
+      <c r="C32" s="17" t="inlineStr">
+        <is>
+          <t>子分类</t>
+        </is>
+      </c>
+      <c r="D32" s="17" t="inlineStr">
+        <is>
+          <t>简介</t>
+        </is>
+      </c>
+      <c r="E32" s="17" t="inlineStr">
+        <is>
+          <t>初步分类</t>
+        </is>
+      </c>
+      <c r="F32" s="17" t="inlineStr">
+        <is>
+          <t>建议操作</t>
+        </is>
+      </c>
+      <c r="G32" s="17" t="inlineStr">
+        <is>
+          <t>优先级</t>
+        </is>
+      </c>
+      <c r="H32" s="17" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="18" t="inlineStr">
+        <is>
+          <t>https://tarot.com</t>
+        </is>
+      </c>
+      <c r="B33" s="18" t="inlineStr">
+        <is>
+          <t>Tarot.com</t>
+        </is>
+      </c>
+      <c r="C33" s="18" t="inlineStr">
+        <is>
+          <t>占星/塔罗</t>
+        </is>
+      </c>
+      <c r="D33" s="18" t="inlineStr">
+        <is>
+          <t>全球最大塔罗+占星平台，每日占卜+星座运势+塔罗解读</t>
+        </is>
+      </c>
+      <c r="E33" s="18" t="inlineStr">
+        <is>
+          <t>新发现</t>
+        </is>
+      </c>
+      <c r="F33" s="18" t="inlineStr">
+        <is>
+          <t>高价值目标</t>
+        </is>
+      </c>
+      <c r="G33" s="18" t="inlineStr">
+        <is>
+          <t>添加到竞品总览并深入研究</t>
+        </is>
+      </c>
+      <c r="H33" s="18" t="inlineStr">
+        <is>
+          <t>P1: 行业顶级平台，数字占卜变现标杆</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="18" t="inlineStr">
+        <is>
+          <t>https://astrologyzone.com</t>
+        </is>
+      </c>
+      <c r="B34" s="18" t="inlineStr">
+        <is>
+          <t>Astrology Zone</t>
+        </is>
+      </c>
+      <c r="C34" s="18" t="inlineStr">
+        <is>
+          <t>占星</t>
+        </is>
+      </c>
+      <c r="D34" s="18" t="inlineStr">
+        <is>
+          <t>Susan Miller创办，全球最权威星座运势网站</t>
+        </is>
+      </c>
+      <c r="E34" s="18" t="inlineStr">
+        <is>
+          <t>新发现</t>
+        </is>
+      </c>
+      <c r="F34" s="18" t="inlineStr">
+        <is>
+          <t>高价值目标</t>
+        </is>
+      </c>
+      <c r="G34" s="18" t="inlineStr">
+        <is>
+          <t>添加到竞品总览并深入研究</t>
+        </is>
+      </c>
+      <c r="H34" s="18" t="inlineStr">
+        <is>
+          <t>P1: Susan Miller个人IP，内容权威性标杆</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="18" t="inlineStr">
+        <is>
+          <t>https://mindvalley.com</t>
+        </is>
+      </c>
+      <c r="B35" s="18" t="inlineStr">
+        <is>
+          <t>Mindvalley</t>
+        </is>
+      </c>
+      <c r="C35" s="18" t="inlineStr">
+        <is>
+          <t>灵性成长/教育</t>
+        </is>
+      </c>
+      <c r="D35" s="18" t="inlineStr">
+        <is>
+          <t>全球最大在线灵性教育平台，课程+博客</t>
+        </is>
+      </c>
+      <c r="E35" s="18" t="inlineStr">
+        <is>
+          <t>新发现</t>
+        </is>
+      </c>
+      <c r="F35" s="18" t="inlineStr">
+        <is>
+          <t>高价值目标</t>
+        </is>
+      </c>
+      <c r="G35" s="18" t="inlineStr">
+        <is>
+          <t>添加到竞品总览并深入研究</t>
+        </is>
+      </c>
+      <c r="H35" s="18" t="inlineStr">
+        <is>
+          <t>P1: 课程变现+内容矩阵的完美结合</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="13" t="inlineStr">
+        <is>
+          <t>https://mindful.org</t>
+        </is>
+      </c>
+      <c r="B36" s="13" t="inlineStr">
+        <is>
+          <t>Mindful</t>
+        </is>
+      </c>
+      <c r="C36" s="13" t="inlineStr">
+        <is>
+          <t>正念/冥想</t>
+        </is>
+      </c>
+      <c r="D36" s="13" t="inlineStr">
+        <is>
+          <t>全球最大正念冥想媒体，杂志+活动</t>
+        </is>
+      </c>
+      <c r="E36" s="13" t="inlineStr">
+        <is>
+          <t>新发现</t>
+        </is>
+      </c>
+      <c r="F36" s="13" t="inlineStr">
+        <is>
+          <t>中等规模</t>
+        </is>
+      </c>
+      <c r="G36" s="13" t="inlineStr">
+        <is>
+          <t>快速浏览参考</t>
+        </is>
+      </c>
+      <c r="H36" s="13" t="inlineStr">
+        <is>
+          <t>P2: 科学化灵性内容的标杆</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="13" t="inlineStr">
+        <is>
+          <t>https://spiritualityhealth.com</t>
+        </is>
+      </c>
+      <c r="B37" s="13" t="inlineStr">
+        <is>
+          <t>Spirituality &amp; Health</t>
+        </is>
+      </c>
+      <c r="C37" s="13" t="inlineStr">
+        <is>
+          <t>灵性健康</t>
+        </is>
+      </c>
+      <c r="D37" s="13" t="inlineStr">
+        <is>
+          <t>灵性健康杂志，涵盖身心灵全方位</t>
+        </is>
+      </c>
+      <c r="E37" s="13" t="inlineStr">
+        <is>
+          <t>新发现</t>
+        </is>
+      </c>
+      <c r="F37" s="13" t="inlineStr">
+        <is>
+          <t>中等规模</t>
+        </is>
+      </c>
+      <c r="G37" s="13" t="inlineStr">
+        <is>
+          <t>快速浏览参考</t>
+        </is>
+      </c>
+      <c r="H37" s="13" t="inlineStr">
+        <is>
+          <t>P2: 灵性健康垂直媒体标杆</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="13" t="inlineStr">
+        <is>
+          <t>https://consciouslifestylemag.com</t>
+        </is>
+      </c>
+      <c r="B38" s="13" t="inlineStr">
+        <is>
+          <t>Conscious Lifestyle Mag</t>
+        </is>
+      </c>
+      <c r="C38" s="13" t="inlineStr">
+        <is>
+          <t>灵性生活方式</t>
+        </is>
+      </c>
+      <c r="D38" s="13" t="inlineStr">
+        <is>
+          <t>灵性生活方式在线杂志</t>
+        </is>
+      </c>
+      <c r="E38" s="13" t="inlineStr">
+        <is>
+          <t>新发现</t>
+        </is>
+      </c>
+      <c r="F38" s="13" t="inlineStr">
+        <is>
+          <t>中等规模</t>
+        </is>
+      </c>
+      <c r="G38" s="13" t="inlineStr">
+        <is>
+          <t>快速浏览参考</t>
+        </is>
+      </c>
+      <c r="H38" s="13" t="inlineStr">
+        <is>
+          <t>P2: 内容深度好，与水晶高度相关</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="18" t="inlineStr">
+        <is>
+          <t>https://foreverconscious.com</t>
+        </is>
+      </c>
+      <c r="B39" s="18" t="inlineStr">
+        <is>
+          <t>Forever Conscious</t>
+        </is>
+      </c>
+      <c r="C39" s="18" t="inlineStr">
+        <is>
+          <t>占星/月亮仪式</t>
+        </is>
+      </c>
+      <c r="D39" s="18" t="inlineStr">
+        <is>
+          <t>星座运势+月相仪式+灵性文章</t>
+        </is>
+      </c>
+      <c r="E39" s="18" t="inlineStr">
+        <is>
+          <t>新发现</t>
+        </is>
+      </c>
+      <c r="F39" s="18" t="inlineStr">
+        <is>
+          <t>高价值目标</t>
+        </is>
+      </c>
+      <c r="G39" s="18" t="inlineStr">
+        <is>
+          <t>添加到竞品总览并深入研究</t>
+        </is>
+      </c>
+      <c r="H39" s="18" t="inlineStr">
+        <is>
+          <t>P1: 事件驱动+月相内容矩阵，最接近Soul Path模式</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="18" t="inlineStr">
+        <is>
+          <t>https://moonomens.com</t>
+        </is>
+      </c>
+      <c r="B40" s="18" t="inlineStr">
+        <is>
+          <t>Moon Omens</t>
+        </is>
+      </c>
+      <c r="C40" s="18" t="inlineStr">
+        <is>
+          <t>月亮仪式/占星</t>
+        </is>
+      </c>
+      <c r="D40" s="18" t="inlineStr">
+        <is>
+          <t>月亮仪式+冥想音频+月相日历</t>
+        </is>
+      </c>
+      <c r="E40" s="18" t="inlineStr">
+        <is>
+          <t>新发现</t>
+        </is>
+      </c>
+      <c r="F40" s="18" t="inlineStr">
+        <is>
+          <t>高价值目标</t>
+        </is>
+      </c>
+      <c r="G40" s="18" t="inlineStr">
+        <is>
+          <t>添加到竞品总览并深入研究</t>
+        </is>
+      </c>
+      <c r="H40" s="18" t="inlineStr">
+        <is>
+          <t>P1: 月相内容矩阵+冥想音频变现，直接可借鉴</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="13" t="inlineStr">
+        <is>
+          <t>https://girlandhermoon.com</t>
+        </is>
+      </c>
+      <c r="B41" s="13" t="inlineStr">
+        <is>
+          <t>Girl and Her Moon</t>
+        </is>
+      </c>
+      <c r="C41" s="13" t="inlineStr">
+        <is>
+          <t>灵性/塔罗</t>
+        </is>
+      </c>
+      <c r="D41" s="13" t="inlineStr">
+        <is>
+          <t>塔罗+占星+自我成长博客</t>
+        </is>
+      </c>
+      <c r="E41" s="13" t="inlineStr">
+        <is>
+          <t>新发现</t>
+        </is>
+      </c>
+      <c r="F41" s="13" t="inlineStr">
+        <is>
+          <t>中等规模</t>
+        </is>
+      </c>
+      <c r="G41" s="13" t="inlineStr">
+        <is>
+          <t>快速浏览参考</t>
+        </is>
+      </c>
+      <c r="H41" s="13" t="inlineStr">
+        <is>
+          <t>P2: 女性灵性社区风格，品牌感强</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="18" t="inlineStr">
+        <is>
+          <t>https://selfgazer.com</t>
+        </is>
+      </c>
+      <c r="B42" s="18" t="inlineStr">
+        <is>
+          <t>Selfgazer</t>
+        </is>
+      </c>
+      <c r="C42" s="18" t="inlineStr">
+        <is>
+          <t>塔罗/占星工具</t>
+        </is>
+      </c>
+      <c r="D42" s="18" t="inlineStr">
+        <is>
+          <t>心理塔罗+出生星图+易经+周运势，全交互工具</t>
+        </is>
+      </c>
+      <c r="E42" s="18" t="inlineStr">
+        <is>
+          <t>新发现</t>
+        </is>
+      </c>
+      <c r="F42" s="18" t="inlineStr">
+        <is>
+          <t>高价值目标</t>
+        </is>
+      </c>
+      <c r="G42" s="18" t="inlineStr">
+        <is>
+          <t>添加到竞品总览并深入研究</t>
+        </is>
+      </c>
+      <c r="H42" s="18" t="inlineStr">
+        <is>
+          <t>P1: 交互式灵性工具标杆，工具变现模式</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="13" t="inlineStr">
+        <is>
+          <t>https://chriscorsini.com</t>
+        </is>
+      </c>
+      <c r="B43" s="13" t="inlineStr">
+        <is>
+          <t>Chris Corsini</t>
+        </is>
+      </c>
+      <c r="C43" s="13" t="inlineStr">
+        <is>
+          <t>塔罗/占星</t>
+        </is>
+      </c>
+      <c r="D43" s="13" t="inlineStr">
+        <is>
+          <t>塔罗+占星洞察，个人IP驱动</t>
+        </is>
+      </c>
+      <c r="E43" s="13" t="inlineStr">
+        <is>
+          <t>新发现</t>
+        </is>
+      </c>
+      <c r="F43" s="13" t="inlineStr">
+        <is>
+          <t>中等规模</t>
+        </is>
+      </c>
+      <c r="G43" s="13" t="inlineStr">
+        <is>
+          <t>快速浏览参考</t>
+        </is>
+      </c>
+      <c r="H43" s="13" t="inlineStr">
+        <is>
+          <t>P2: 个人IP+咨询变现模式</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="13" t="inlineStr">
+        <is>
+          <t>https://spiritualawakeningprocess.com</t>
+        </is>
+      </c>
+      <c r="B44" s="13" t="inlineStr">
+        <is>
+          <t>Spiritual Awakening Process</t>
+        </is>
+      </c>
+      <c r="C44" s="13" t="inlineStr">
+        <is>
+          <t>灵性觉醒</t>
+        </is>
+      </c>
+      <c r="D44" s="13" t="inlineStr">
+        <is>
+          <t>灵性觉醒方法论博客，以臣服/接纳为核心</t>
+        </is>
+      </c>
+      <c r="E44" s="13" t="inlineStr">
+        <is>
+          <t>新发现</t>
+        </is>
+      </c>
+      <c r="F44" s="13" t="inlineStr">
+        <is>
+          <t>中等规模</t>
+        </is>
+      </c>
+      <c r="G44" s="13" t="inlineStr">
+        <is>
+          <t>快速浏览参考</t>
+        </is>
+      </c>
+      <c r="H44" s="13" t="inlineStr">
+        <is>
+          <t>P2: 灵性觉醒垂直内容深度好</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="13" t="inlineStr">
+        <is>
+          <t>https://awakeningself.com</t>
+        </is>
+      </c>
+      <c r="B45" s="13" t="inlineStr">
+        <is>
+          <t>Awakening Self</t>
+        </is>
+      </c>
+      <c r="C45" s="13" t="inlineStr">
+        <is>
+          <t>灵性觉醒</t>
+        </is>
+      </c>
+      <c r="D45" s="13" t="inlineStr">
+        <is>
+          <t>灵性觉醒+个人成长博客</t>
+        </is>
+      </c>
+      <c r="E45" s="13" t="inlineStr">
+        <is>
+          <t>新发现</t>
+        </is>
+      </c>
+      <c r="F45" s="13" t="inlineStr">
+        <is>
+          <t>小型/垂直</t>
+        </is>
+      </c>
+      <c r="G45" s="13" t="inlineStr">
+        <is>
+          <t>可选参考</t>
+        </is>
+      </c>
+      <c r="H45" s="13" t="inlineStr">
+        <is>
+          <t>P3: 心理+灵性结合的写作风格</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="13" t="inlineStr">
+        <is>
+          <t>https://thetarotlady.com</t>
+        </is>
+      </c>
+      <c r="B46" s="13" t="inlineStr">
+        <is>
+          <t>The Tarot Lady</t>
+        </is>
+      </c>
+      <c r="C46" s="13" t="inlineStr">
+        <is>
+          <t>塔罗</t>
+        </is>
+      </c>
+      <c r="D46" s="13" t="inlineStr">
+        <is>
+          <t>专业塔罗博客，面向塔罗爱好者</t>
+        </is>
+      </c>
+      <c r="E46" s="13" t="inlineStr">
+        <is>
+          <t>新发现</t>
+        </is>
+      </c>
+      <c r="F46" s="13" t="inlineStr">
+        <is>
+          <t>小型/垂直</t>
+        </is>
+      </c>
+      <c r="G46" s="13" t="inlineStr">
+        <is>
+          <t>可选参考</t>
+        </is>
+      </c>
+      <c r="H46" s="13" t="inlineStr">
+        <is>
+          <t>P3: 垂直塔罗领域的标杆</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="13" t="inlineStr">
+        <is>
+          <t>https://jessicaadams.com</t>
+        </is>
+      </c>
+      <c r="B47" s="13" t="inlineStr">
+        <is>
+          <t>Jessica Adams</t>
+        </is>
+      </c>
+      <c r="C47" s="13" t="inlineStr">
+        <is>
+          <t>占星</t>
+        </is>
+      </c>
+      <c r="D47" s="13" t="inlineStr">
+        <is>
+          <t>心理占星师博客，星座运势+灵性</t>
+        </is>
+      </c>
+      <c r="E47" s="13" t="inlineStr">
+        <is>
+          <t>新发现</t>
+        </is>
+      </c>
+      <c r="F47" s="13" t="inlineStr">
+        <is>
+          <t>小型/垂直</t>
+        </is>
+      </c>
+      <c r="G47" s="13" t="inlineStr">
+        <is>
+          <t>可选参考</t>
+        </is>
+      </c>
+      <c r="H47" s="13" t="inlineStr">
+        <is>
+          <t>P3: 占星师个人IP模式</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="13" t="inlineStr">
+        <is>
+          <t>https://ommagazine.com</t>
+        </is>
+      </c>
+      <c r="B48" s="13" t="inlineStr">
+        <is>
+          <t>OM Yoga Magazine</t>
+        </is>
+      </c>
+      <c r="C48" s="13" t="inlineStr">
+        <is>
+          <t>瑜伽/正念</t>
+        </is>
+      </c>
+      <c r="D48" s="13" t="inlineStr">
+        <is>
+          <t>瑜伽+冥想+正念在线杂志</t>
+        </is>
+      </c>
+      <c r="E48" s="13" t="inlineStr">
+        <is>
+          <t>新发现</t>
+        </is>
+      </c>
+      <c r="F48" s="13" t="inlineStr">
+        <is>
+          <t>小型/垂直</t>
+        </is>
+      </c>
+      <c r="G48" s="13" t="inlineStr">
+        <is>
+          <t>可选参考</t>
+        </is>
+      </c>
+      <c r="H48" s="13" t="inlineStr">
+        <is>
+          <t>P3: 瑜伽垂直杂志，内容广</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="13" t="inlineStr">
+        <is>
+          <t>https://meditationmag.com</t>
+        </is>
+      </c>
+      <c r="B49" s="13" t="inlineStr">
+        <is>
+          <t>Meditation Magazine</t>
+        </is>
+      </c>
+      <c r="C49" s="13" t="inlineStr">
+        <is>
+          <t>冥想</t>
+        </is>
+      </c>
+      <c r="D49" s="13" t="inlineStr">
+        <is>
+          <t>冥想专业杂志，印刷+数字版</t>
+        </is>
+      </c>
+      <c r="E49" s="13" t="inlineStr">
+        <is>
+          <t>新发现</t>
+        </is>
+      </c>
+      <c r="F49" s="13" t="inlineStr">
+        <is>
+          <t>小型/垂直</t>
+        </is>
+      </c>
+      <c r="G49" s="13" t="inlineStr">
+        <is>
+          <t>可选参考</t>
+        </is>
+      </c>
+      <c r="H49" s="13" t="inlineStr">
+        <is>
+          <t>P3: 冥想垂直杂志</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="13" t="inlineStr">
+        <is>
+          <t>https://theholisticingredient.com</t>
+        </is>
+      </c>
+      <c r="B50" s="13" t="inlineStr">
+        <is>
+          <t>The Holistic Ingredient</t>
+        </is>
+      </c>
+      <c r="C50" s="13" t="inlineStr">
+        <is>
+          <t>整体健康</t>
+        </is>
+      </c>
+      <c r="D50" s="13" t="inlineStr">
+        <is>
+          <t>整体健康博客，含水晶内容</t>
+        </is>
+      </c>
+      <c r="E50" s="13" t="inlineStr">
+        <is>
+          <t>新发现</t>
+        </is>
+      </c>
+      <c r="F50" s="13" t="inlineStr">
+        <is>
+          <t>小型/垂直</t>
+        </is>
+      </c>
+      <c r="G50" s="13" t="inlineStr">
+        <is>
+          <t>可选参考</t>
+        </is>
+      </c>
+      <c r="H50" s="13" t="inlineStr">
+        <is>
+          <t>P3: 整体健康+水晶交叉内容</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="13" t="inlineStr">
+        <is>
+          <t>https://themysticalmoons.com</t>
+        </is>
+      </c>
+      <c r="B51" s="13" t="inlineStr">
+        <is>
+          <t>The Mystical Moons</t>
+        </is>
+      </c>
+      <c r="C51" s="13" t="inlineStr">
+        <is>
+          <t>水晶/灵性</t>
+        </is>
+      </c>
+      <c r="D51" s="13" t="inlineStr">
+        <is>
+          <t>水晶疗愈+灵性博客</t>
+        </is>
+      </c>
+      <c r="E51" s="13" t="inlineStr">
+        <is>
+          <t>新发现</t>
+        </is>
+      </c>
+      <c r="F51" s="13" t="inlineStr">
+        <is>
+          <t>小型/垂直</t>
+        </is>
+      </c>
+      <c r="G51" s="13" t="inlineStr">
+        <is>
+          <t>可选参考</t>
+        </is>
+      </c>
+      <c r="H51" s="13" t="inlineStr">
+        <is>
+          <t>P3: 水晶内容较多的小型灵性站</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A31:H31"/>
+    <mergeCell ref="A1:H1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2040,7 +4883,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2578,13 +5421,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2924,6 +5767,276 @@
       </c>
       <c r="F12" s="4" t="inlineStr"/>
     </row>
+    <row r="13">
+      <c r="A13" s="13" t="inlineStr">
+        <is>
+          <t>P1 - 重要</t>
+        </is>
+      </c>
+      <c r="B13" s="13" t="inlineStr">
+        <is>
+          <t>healingcrystals.com</t>
+        </is>
+      </c>
+      <c r="C13" s="13" t="inlineStr">
+        <is>
+          <t>1. 网站架构
+2. 水晶百科内容模式
+3. 批发+零售模式</t>
+        </is>
+      </c>
+      <c r="D13" s="13" t="inlineStr">
+        <is>
+          <t>内容架构参考</t>
+        </is>
+      </c>
+      <c r="E13" s="13" t="inlineStr">
+        <is>
+          <t>待开始</t>
+        </is>
+      </c>
+      <c r="F13" s="13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="13" t="inlineStr">
+        <is>
+          <t>P1 - 重要</t>
+        </is>
+      </c>
+      <c r="B14" s="13" t="inlineStr">
+        <is>
+          <t>rockparadise.com</t>
+        </is>
+      </c>
+      <c r="C14" s="13" t="inlineStr">
+        <is>
+          <t>1. 产品线规划
+2. 产品分类方式
+3. 内容到产品转化</t>
+        </is>
+      </c>
+      <c r="D14" s="13" t="inlineStr">
+        <is>
+          <t>产品架构参考</t>
+        </is>
+      </c>
+      <c r="E14" s="13" t="inlineStr">
+        <is>
+          <t>待开始</t>
+        </is>
+      </c>
+      <c r="F14" s="13" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="13" t="inlineStr">
+        <is>
+          <t>P1 - 重要</t>
+        </is>
+      </c>
+      <c r="B15" s="13" t="inlineStr">
+        <is>
+          <t>moonrisecrystals.com</t>
+        </is>
+      </c>
+      <c r="C15" s="13" t="inlineStr">
+        <is>
+          <t>1. 伦理采购叙事
+2. 水晶百科内容
+3. SEO策略</t>
+        </is>
+      </c>
+      <c r="D15" s="13" t="inlineStr">
+        <is>
+          <t>差异化定位参考</t>
+        </is>
+      </c>
+      <c r="E15" s="13" t="inlineStr">
+        <is>
+          <t>待开始</t>
+        </is>
+      </c>
+      <c r="F15" s="13" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="13" t="inlineStr">
+        <is>
+          <t>P0 - 最先</t>
+        </is>
+      </c>
+      <c r="B16" s="13" t="inlineStr">
+        <is>
+          <t>tarot.com</t>
+        </is>
+      </c>
+      <c r="C16" s="13" t="inlineStr">
+        <is>
+          <t>1. 数字占卜变现模式
+2. 内容矩阵架构
+3. 订阅+虚拟服务漏斗</t>
+        </is>
+      </c>
+      <c r="D16" s="13" t="inlineStr">
+        <is>
+          <t>数字占卜变现+内容架构</t>
+        </is>
+      </c>
+      <c r="E16" s="13" t="inlineStr">
+        <is>
+          <t>待开始</t>
+        </is>
+      </c>
+      <c r="F16" s="13" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="13" t="inlineStr">
+        <is>
+          <t>P0 - 最先</t>
+        </is>
+      </c>
+      <c r="B17" s="13" t="inlineStr">
+        <is>
+          <t>foreverconscious.com</t>
+        </is>
+      </c>
+      <c r="C17" s="13" t="inlineStr">
+        <is>
+          <t>1. 月相事件驱动内容
+2. 内容矩阵设计
+3. SEO策略</t>
+        </is>
+      </c>
+      <c r="D17" s="13" t="inlineStr">
+        <is>
+          <t>事件驱动+月相矩阵</t>
+        </is>
+      </c>
+      <c r="E17" s="13" t="inlineStr">
+        <is>
+          <t>待开始</t>
+        </is>
+      </c>
+      <c r="F17" s="13" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="13" t="inlineStr">
+        <is>
+          <t>P0 - 最先</t>
+        </is>
+      </c>
+      <c r="B18" s="13" t="inlineStr">
+        <is>
+          <t>moonomens.com</t>
+        </is>
+      </c>
+      <c r="C18" s="13" t="inlineStr">
+        <is>
+          <t>1. 月相内容+冥想音频
+2. 数字产品变现
+3. 可打印日志设计</t>
+        </is>
+      </c>
+      <c r="D18" s="13" t="inlineStr">
+        <is>
+          <t>音频+日志变现</t>
+        </is>
+      </c>
+      <c r="E18" s="13" t="inlineStr">
+        <is>
+          <t>待开始</t>
+        </is>
+      </c>
+      <c r="F18" s="13" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="13" t="inlineStr">
+        <is>
+          <t>P1 - 重要</t>
+        </is>
+      </c>
+      <c r="B19" s="13" t="inlineStr">
+        <is>
+          <t>selfgazer.com</t>
+        </is>
+      </c>
+      <c r="C19" s="13" t="inlineStr">
+        <is>
+          <t>1. 交互式塔罗工具
+2. 星图分析工具
+3. 工具变现模式</t>
+        </is>
+      </c>
+      <c r="D19" s="13" t="inlineStr">
+        <is>
+          <t>交互灵性工具</t>
+        </is>
+      </c>
+      <c r="E19" s="13" t="inlineStr">
+        <is>
+          <t>待开始</t>
+        </is>
+      </c>
+      <c r="F19" s="13" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="13" t="inlineStr">
+        <is>
+          <t>P1 - 重要</t>
+        </is>
+      </c>
+      <c r="B20" s="13" t="inlineStr">
+        <is>
+          <t>mindvalley.com</t>
+        </is>
+      </c>
+      <c r="C20" s="13" t="inlineStr">
+        <is>
+          <t>1. 课程+内容矩阵结合
+2. 会员变现模式
+3. 品牌调性</t>
+        </is>
+      </c>
+      <c r="D20" s="13" t="inlineStr">
+        <is>
+          <t>课程变现+内容矩阵</t>
+        </is>
+      </c>
+      <c r="E20" s="13" t="inlineStr">
+        <is>
+          <t>待开始</t>
+        </is>
+      </c>
+      <c r="F20" s="13" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="13" t="inlineStr">
+        <is>
+          <t>P1 - 重要</t>
+        </is>
+      </c>
+      <c r="B21" s="13" t="inlineStr">
+        <is>
+          <t>astrologyzone.com</t>
+        </is>
+      </c>
+      <c r="C21" s="13" t="inlineStr">
+        <is>
+          <t>1. 个人IP打造
+2. 月度内容节奏
+3. 订阅模式</t>
+        </is>
+      </c>
+      <c r="D21" s="13" t="inlineStr">
+        <is>
+          <t>IP+订阅变现</t>
+        </is>
+      </c>
+      <c r="E21" s="13" t="inlineStr">
+        <is>
+          <t>待开始</t>
+        </is>
+      </c>
+      <c r="F21" s="13" t="inlineStr"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:F1"/>
